--- a/data/trans_orig/P62-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P62-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2007</t>
+          <t>Población según si percibe alguna pensión en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76939</t>
+          <t>78764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96497</t>
+          <t>96407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>51438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113293</t>
+          <t>114124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142974</t>
+          <t>142799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61452</t>
+          <t>61627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91133</t>
+          <t>90302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84924</t>
+          <t>84200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87892</t>
+          <t>87811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118775</t>
+          <t>119951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>27455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121205</t>
+          <t>121088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115481</t>
+          <t>114305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146364</t>
+          <t>146445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106659</t>
+          <t>106298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128342</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122982</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156209</t>
+          <t>154406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>54110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>78573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>94591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113350</t>
+          <t>115153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146577</t>
+          <t>147463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>340610</t>
+          <t>340102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>385640</t>
+          <t>383378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95132</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131337</t>
+          <t>131149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444814</t>
+          <t>446854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505700</t>
+          <t>505976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141623</t>
+          <t>143885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186653</t>
+          <t>187161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274043</t>
+          <t>274231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>310875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426943</t>
+          <t>426667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487829</t>
+          <t>485789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71098</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96394</t>
+          <t>95050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>83668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119697</t>
+          <t>119953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164691</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209823</t>
+          <t>205552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>67737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91689</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235715</t>
+          <t>235459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>271071</t>
+          <t>271744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308376</t>
+          <t>312647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353508</t>
+          <t>355728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245822</t>
+          <t>245619</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302654</t>
+          <t>305757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>253743</t>
+          <t>255342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>315559</t>
+          <t>315866</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276247</t>
+          <t>276972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290070</t>
+          <t>289596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>945256</t>
+          <t>942153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1002088</t>
+          <t>1002291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1227297</t>
+          <t>1226990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1289113</t>
+          <t>1287514</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>703479</t>
+          <t>704938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>778050</t>
+          <t>775899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>538352</t>
+          <t>540050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617338</t>
+          <t>621747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1257545</t>
+          <t>1263898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1377472</t>
+          <t>1378509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>578421</t>
+          <t>580572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652992</t>
+          <t>651533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1728129</t>
+          <t>1723720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1807115</t>
+          <t>1805417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2324467</t>
+          <t>2323430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2444394</t>
+          <t>2438041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2012</t>
+          <t>Población según si percibe alguna pensión en 2012 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56962</t>
+          <t>57317</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81640</t>
+          <t>82126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>27874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124576</t>
+          <t>125193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75361</t>
+          <t>75006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70213</t>
+          <t>70937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91524</t>
+          <t>91147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126768</t>
+          <t>126151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160416</t>
+          <t>159917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82310</t>
+          <t>82283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>108065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>50597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114636</t>
+          <t>113662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153075</t>
+          <t>154011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51750</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77992</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116958</t>
+          <t>116394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140628</t>
+          <t>140289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174218</t>
+          <t>173282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212657</t>
+          <t>213631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164528</t>
+          <t>166652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203445</t>
+          <t>204788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>47696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71758</t>
+          <t>72595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221572</t>
+          <t>221637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268002</t>
+          <t>267624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184297</t>
+          <t>182173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73798</t>
+          <t>72961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226380</t>
+          <t>226758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272810</t>
+          <t>272745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>322205</t>
+          <t>321508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>379375</t>
+          <t>378406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95048</t>
+          <t>97570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136989</t>
+          <t>136997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>432104</t>
+          <t>432550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497962</t>
+          <t>502291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>343249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>399450</t>
+          <t>400147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323650</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365591</t>
+          <t>363069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684331</t>
+          <t>680002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750189</t>
+          <t>749743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135663</t>
+          <t>132728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170806</t>
+          <t>171607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202999</t>
+          <t>201841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>250550</t>
+          <t>249873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346899</t>
+          <t>347177</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>409667</t>
+          <t>408473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>184165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220109</t>
+          <t>223044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326645</t>
+          <t>327322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374196</t>
+          <t>375354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>523299</t>
+          <t>524493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586067</t>
+          <t>585789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>242457</t>
+          <t>239975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302147</t>
+          <t>298189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257775</t>
+          <t>257216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317744</t>
+          <t>318287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232816</t>
+          <t>233152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250579</t>
+          <t>250169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>797817</t>
+          <t>801775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>857507</t>
+          <t>859989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1041807</t>
+          <t>1041264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1101776</t>
+          <t>1102335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>827474</t>
+          <t>820807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>917680</t>
+          <t>915912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>700615</t>
+          <t>701867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>793232</t>
+          <t>797363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1553842</t>
+          <t>1552310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1686184</t>
+          <t>1687256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1060783</t>
+          <t>1062551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1150989</t>
+          <t>1157656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1776133</t>
+          <t>1772002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1868750</t>
+          <t>1867498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2861645</t>
+          <t>2860573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2993987</t>
+          <t>2995519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2016</t>
+          <t>Población según si percibe alguna pensión en 2016 (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84359</t>
+          <t>86363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109526</t>
+          <t>109841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131380</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164529</t>
+          <t>164365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39913</t>
+          <t>39598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67945</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>91993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115466</t>
+          <t>115630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148615</t>
+          <t>149130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68163</t>
+          <t>67848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52643</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100919</t>
+          <t>101225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135237</t>
+          <t>135795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>42286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65032</t>
+          <t>65347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128518</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152341</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179119</t>
+          <t>178561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213437</t>
+          <t>213131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157458</t>
+          <t>158769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191200</t>
+          <t>194232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38321</t>
+          <t>38905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>59531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203600</t>
+          <t>202887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243859</t>
+          <t>243026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110764</t>
+          <t>107732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144506</t>
+          <t>143195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>38370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>58996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156006</t>
+          <t>156839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196265</t>
+          <t>196978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319132</t>
+          <t>320508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373983</t>
+          <t>371897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126740</t>
+          <t>126495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166562</t>
+          <t>166693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>458735</t>
+          <t>456380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>526473</t>
+          <t>523263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283500</t>
+          <t>285586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338351</t>
+          <t>336975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286630</t>
+          <t>286499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326452</t>
+          <t>326697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>584202</t>
+          <t>587412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>651940</t>
+          <t>654295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172474</t>
+          <t>171762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>214768</t>
+          <t>213255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186697</t>
+          <t>186807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232363</t>
+          <t>232036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371121</t>
+          <t>372513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>430419</t>
+          <t>434095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210120</t>
+          <t>211633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252414</t>
+          <t>253126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302881</t>
+          <t>303208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348547</t>
+          <t>348437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529713</t>
+          <t>526037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589011</t>
+          <t>587619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>216539</t>
+          <t>222264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278178</t>
+          <t>279182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>227106</t>
+          <t>227096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289774</t>
+          <t>291871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257464</t>
+          <t>257116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269241</t>
+          <t>269098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>775118</t>
+          <t>774114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>836757</t>
+          <t>831032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1036759</t>
+          <t>1034662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1099427</t>
+          <t>1099437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>853951</t>
+          <t>856629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>943303</t>
+          <t>942165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>693042</t>
+          <t>690713</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>787518</t>
+          <t>787195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1576513</t>
+          <t>1570645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1707991</t>
+          <t>1696451</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>996903</t>
+          <t>998041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1086255</t>
+          <t>1083577</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1663831</t>
+          <t>1664154</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1758307</t>
+          <t>1760636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2683564</t>
+          <t>2695104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2815042</t>
+          <t>2820910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2023</t>
+          <t>Población según si percibe alguna pensión en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>90941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114642</t>
+          <t>114751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55290</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74233</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153068</t>
+          <t>152515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182670</t>
+          <t>183052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>62358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74669</t>
+          <t>74308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>100206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130190</t>
+          <t>130743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98362</t>
+          <t>97223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118110</t>
+          <t>117378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>69729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155293</t>
+          <t>154603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>183148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29727</t>
+          <t>30459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76357</t>
+          <t>76597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93120</t>
+          <t>92976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120831</t>
+          <t>121521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>118570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141369</t>
+          <t>141201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43815</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58612</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169159</t>
+          <t>168151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196128</t>
+          <t>195755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37207</t>
+          <t>37375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58193</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49884</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76147</t>
+          <t>76520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103116</t>
+          <t>104124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267444</t>
+          <t>267062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317937</t>
+          <t>319316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197230</t>
+          <t>196225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>470614</t>
+          <t>464392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517767</t>
+          <t>517364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816298</t>
+          <t>816872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155933</t>
+          <t>154554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206426</t>
+          <t>206808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>87087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354249</t>
+          <t>355254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209052</t>
+          <t>208478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507583</t>
+          <t>507986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125501</t>
+          <t>127406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155972</t>
+          <t>155272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204906</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238186</t>
+          <t>238951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342313</t>
+          <t>339894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386761</t>
+          <t>385213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78833</t>
+          <t>79533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109304</t>
+          <t>107399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>226546</t>
+          <t>225781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>259826</t>
+          <t>259958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312776</t>
+          <t>314324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357224</t>
+          <t>359643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177961</t>
+          <t>177384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219885</t>
+          <t>219656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186751</t>
+          <t>187757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230078</t>
+          <t>232850</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217899</t>
+          <t>218343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232185</t>
+          <t>232020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>536857</t>
+          <t>537086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>578781</t>
+          <t>579358</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>764419</t>
+          <t>761647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>807746</t>
+          <t>806740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>741598</t>
+          <t>744637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>833951</t>
+          <t>837099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>786978</t>
+          <t>789798</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1270673</t>
+          <t>1265640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1590579</t>
+          <t>1585293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2057706</t>
+          <t>2133940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592192</t>
+          <t>589044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>684545</t>
+          <t>681506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>854225</t>
+          <t>859258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1337920</t>
+          <t>1335100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1493335</t>
+          <t>1417101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1960462</t>
+          <t>1965748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P62-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78764</t>
+          <t>78411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96407</t>
+          <t>97148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114124</t>
+          <t>114592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142799</t>
+          <t>142999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57239</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61627</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90302</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68722</t>
+          <t>68842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84200</t>
+          <t>84560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87811</t>
+          <t>89082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119951</t>
+          <t>119512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101805</t>
+          <t>102024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121088</t>
+          <t>121136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114305</t>
+          <t>114744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146445</t>
+          <t>145174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106298</t>
+          <t>106400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128777</t>
+          <t>128086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122096</t>
+          <t>123314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154406</t>
+          <t>156984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54110</t>
+          <t>54008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78573</t>
+          <t>78903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94591</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115153</t>
+          <t>112575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>340102</t>
+          <t>340235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>383378</t>
+          <t>382722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>97492</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131149</t>
+          <t>131547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446854</t>
+          <t>443271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505976</t>
+          <t>504278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143885</t>
+          <t>144541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187161</t>
+          <t>187028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274231</t>
+          <t>273833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310875</t>
+          <t>307888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426667</t>
+          <t>428365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>485789</t>
+          <t>489372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>69714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>95667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83668</t>
+          <t>83767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119953</t>
+          <t>117653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162471</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205552</t>
+          <t>205984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67737</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92304</t>
+          <t>93073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235459</t>
+          <t>237759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>271744</t>
+          <t>271645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312647</t>
+          <t>312215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355728</t>
+          <t>355689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245619</t>
+          <t>247225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305757</t>
+          <t>306632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255342</t>
+          <t>256616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>315866</t>
+          <t>315594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276972</t>
+          <t>275612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289596</t>
+          <t>289631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>942153</t>
+          <t>941278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1002291</t>
+          <t>1000685</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1226990</t>
+          <t>1227262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1287514</t>
+          <t>1286240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>704938</t>
+          <t>702168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>775899</t>
+          <t>777031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>540050</t>
+          <t>538248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621747</t>
+          <t>617994</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1263898</t>
+          <t>1260130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1378509</t>
+          <t>1369777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580572</t>
+          <t>579440</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651533</t>
+          <t>654303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1723720</t>
+          <t>1727473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1805417</t>
+          <t>1807219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2323430</t>
+          <t>2332162</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2438041</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57317</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>81918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48084</t>
+          <t>49061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91427</t>
+          <t>89727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125193</t>
+          <t>123705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50197</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75006</t>
+          <t>74202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>69960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91147</t>
+          <t>91471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126151</t>
+          <t>127639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159917</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82283</t>
+          <t>82341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>109764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26702</t>
+          <t>26833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113662</t>
+          <t>113162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154011</t>
+          <t>151268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78019</t>
+          <t>77961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116394</t>
+          <t>116733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140289</t>
+          <t>140158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173282</t>
+          <t>176025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213631</t>
+          <t>214131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166652</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204788</t>
+          <t>204985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47696</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221637</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267624</t>
+          <t>269045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>143840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>184217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>74233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97860</t>
+          <t>98426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226758</t>
+          <t>225337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272745</t>
+          <t>272663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>321508</t>
+          <t>323553</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>378406</t>
+          <t>378097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97570</t>
+          <t>97563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>137235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>432550</t>
+          <t>432629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>502291</t>
+          <t>500688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343249</t>
+          <t>343558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>400147</t>
+          <t>398102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323642</t>
+          <t>323404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363069</t>
+          <t>363076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680002</t>
+          <t>681605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749743</t>
+          <t>749664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132728</t>
+          <t>137222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171607</t>
+          <t>174932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201841</t>
+          <t>203790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249873</t>
+          <t>250174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347177</t>
+          <t>347887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408473</t>
+          <t>411164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184165</t>
+          <t>180840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>223044</t>
+          <t>218550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327322</t>
+          <t>327021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375354</t>
+          <t>373405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524493</t>
+          <t>521802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>585789</t>
+          <t>585079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>239975</t>
+          <t>241541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>298189</t>
+          <t>297921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257216</t>
+          <t>257427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318287</t>
+          <t>317843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233152</t>
+          <t>233024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250169</t>
+          <t>250097</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>801775</t>
+          <t>802043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>859989</t>
+          <t>858423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1041264</t>
+          <t>1041708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1102335</t>
+          <t>1102124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>820807</t>
+          <t>823896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>915912</t>
+          <t>915223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>701867</t>
+          <t>696860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>797363</t>
+          <t>796496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1552310</t>
+          <t>1549610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1687256</t>
+          <t>1680670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1062551</t>
+          <t>1063240</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1157656</t>
+          <t>1154567</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1772002</t>
+          <t>1772869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1867498</t>
+          <t>1872505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2860573</t>
+          <t>2867159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2995519</t>
+          <t>2998219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86363</t>
+          <t>86332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109841</t>
+          <t>109484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38563</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62930</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130865</t>
+          <t>131116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164365</t>
+          <t>164561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115630</t>
+          <t>115434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149130</t>
+          <t>148879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67848</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>90136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101225</t>
+          <t>100736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135795</t>
+          <t>135623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42286</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65347</t>
+          <t>66574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131095</t>
+          <t>130190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154104</t>
+          <t>153678</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178561</t>
+          <t>178733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213131</t>
+          <t>213620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158769</t>
+          <t>157180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194232</t>
+          <t>192639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38905</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59531</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202887</t>
+          <t>203536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243026</t>
+          <t>242487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107732</t>
+          <t>109325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143195</t>
+          <t>144784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38370</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>58376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156839</t>
+          <t>157378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196978</t>
+          <t>196329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>320508</t>
+          <t>318930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>371897</t>
+          <t>372838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126495</t>
+          <t>126344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166693</t>
+          <t>166712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>456380</t>
+          <t>456797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523263</t>
+          <t>524304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285586</t>
+          <t>284645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336975</t>
+          <t>338553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286499</t>
+          <t>286480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326697</t>
+          <t>326848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587412</t>
+          <t>586371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>654295</t>
+          <t>653878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171762</t>
+          <t>175051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213255</t>
+          <t>215618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186807</t>
+          <t>185843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232036</t>
+          <t>232417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372513</t>
+          <t>370044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434095</t>
+          <t>431952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211633</t>
+          <t>209270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>253126</t>
+          <t>249837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>303208</t>
+          <t>302827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348437</t>
+          <t>349401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>526037</t>
+          <t>528180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>587619</t>
+          <t>590088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222264</t>
+          <t>220008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>277909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>227096</t>
+          <t>229586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>291871</t>
+          <t>287175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257116</t>
+          <t>257376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269098</t>
+          <t>269436</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>774114</t>
+          <t>775387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>831032</t>
+          <t>833288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1034662</t>
+          <t>1039358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1099437</t>
+          <t>1096947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>856629</t>
+          <t>854707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>942165</t>
+          <t>941448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>690713</t>
+          <t>694354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>787195</t>
+          <t>790635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1570645</t>
+          <t>1575037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1696451</t>
+          <t>1707934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>998041</t>
+          <t>998758</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1083577</t>
+          <t>1085499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1664154</t>
+          <t>1660714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1760636</t>
+          <t>1756995</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2695104</t>
+          <t>2683621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2820910</t>
+          <t>2816518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>103603</t>
+          <t>116941</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90941</t>
+          <t>105489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114751</t>
+          <t>127949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55651</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>83057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>167963</t>
+          <t>190231</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152515</t>
+          <t>175825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183052</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>50865</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>39857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62358</t>
+          <t>62317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>76123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>66356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74308</t>
+          <t>86891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115295</t>
+          <t>126988</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>110128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130743</t>
+          <t>141394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129959</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283258</t>
+          <t>317219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>116743</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97223</t>
+          <t>105685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117378</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>69771</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>59695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69729</t>
+          <t>79529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>168453</t>
+          <t>186514</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154603</t>
+          <t>172113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183148</t>
+          <t>203514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40065</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30459</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>55767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67606</t>
+          <t>77707</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58559</t>
+          <t>67949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76597</t>
+          <t>87783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>107671</t>
+          <t>122416</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92976</t>
+          <t>105416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121521</t>
+          <t>136817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147837</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>147478</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>147478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>147478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>276124</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>276124</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>276124</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>143408</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118570</t>
+          <t>130557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>155420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>48667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>65298</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>182757</t>
+          <t>200110</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168151</t>
+          <t>185269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195755</t>
+          <t>215338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37375</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60006</t>
+          <t>68642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42068</t>
+          <t>47825</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>89518</t>
+          <t>103616</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76520</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104124</t>
+          <t>118457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>199199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>104527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>295144</t>
+          <t>321545</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267062</t>
+          <t>296372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319316</t>
+          <t>345529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>332846</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196225</t>
+          <t>124107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>464392</t>
+          <t>154953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>627991</t>
+          <t>460723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517364</t>
+          <t>435081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816872</t>
+          <t>491716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>178726</t>
+          <t>188264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154554</t>
+          <t>164280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206808</t>
+          <t>213437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>218633</t>
+          <t>242835</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87087</t>
+          <t>227059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355254</t>
+          <t>257905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>397359</t>
+          <t>431099</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208478</t>
+          <t>400106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507986</t>
+          <t>456741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>473870</t>
+          <t>509809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>551479</t>
+          <t>382012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1025350</t>
+          <t>891822</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>141088</t>
+          <t>150965</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>127406</t>
+          <t>135143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155272</t>
+          <t>167957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>221446</t>
+          <t>242323</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>224361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238951</t>
+          <t>261138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>362534</t>
+          <t>393288</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339894</t>
+          <t>368067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385213</t>
+          <t>416409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93717</t>
+          <t>106467</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79533</t>
+          <t>89475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>122289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>243286</t>
+          <t>273433</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>225781</t>
+          <t>254618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>259958</t>
+          <t>291395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>337003</t>
+          <t>379900</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314324</t>
+          <t>356779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359643</t>
+          <t>405121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234805</t>
+          <t>257432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>515756</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>515756</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>515756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>773188</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>773188</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>773188</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>197340</t>
+          <t>212714</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177384</t>
+          <t>192250</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219656</t>
+          <t>234540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>208191</t>
+          <t>223140</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187757</t>
+          <t>199395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232850</t>
+          <t>248708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>226905</t>
+          <t>223759</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218343</t>
+          <t>214817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232020</t>
+          <t>228929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>559402</t>
+          <t>626855</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537086</t>
+          <t>605029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579358</t>
+          <t>647319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>786306</t>
+          <t>850614</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>761647</t>
+          <t>825046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>806740</t>
+          <t>874359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>237755</t>
+          <t>234185</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237755</t>
+          <t>234185</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237755</t>
+          <t>234185</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>756742</t>
+          <t>839569</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>756742</t>
+          <t>839569</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>756742</t>
+          <t>839569</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>994497</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>994497</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>994497</t>
+          <t>1073754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>789584</t>
+          <t>860028</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>744637</t>
+          <t>818737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>837099</t>
+          <t>902223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>928305</t>
+          <t>793978</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>789798</t>
+          <t>755512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1265640</t>
+          <t>829932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1717889</t>
+          <t>1654005</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1585293</t>
+          <t>1597595</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2133940</t>
+          <t>1709268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>636559</t>
+          <t>669855</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589044</t>
+          <t>627660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>681506</t>
+          <t>711146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1196593</t>
+          <t>1344777</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>859258</t>
+          <t>1308823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1335100</t>
+          <t>1383243</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1833152</t>
+          <t>2014633</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1417101</t>
+          <t>1959370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1965748</t>
+          <t>2071043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1426143</t>
+          <t>1529883</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1426143</t>
+          <t>1529883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1426143</t>
+          <t>1529883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2124898</t>
+          <t>2138755</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2124898</t>
+          <t>2138755</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2124898</t>
+          <t>2138755</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3551041</t>
+          <t>3668638</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3551041</t>
+          <t>3668638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3551041</t>
+          <t>3668638</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
